--- a/事業計画_Ver1.6.xlsx
+++ b/事業計画_Ver1.6.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -228,14 +228,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2353,23 +2356,23 @@
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="37">
+      <c r="C28" s="39">
         <f>SUM(C21:C27)</f>
         <v/>
       </c>
-      <c r="D28" s="37">
+      <c r="D28" s="39">
         <f>SUM(D21:D27)</f>
         <v/>
       </c>
-      <c r="E28" s="37">
+      <c r="E28" s="39">
         <f>SUM(E21:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="37">
+      <c r="F28" s="39">
         <f>SUM(F21:F27)</f>
         <v/>
       </c>
-      <c r="G28" s="37">
+      <c r="G28" s="39">
         <f>SUM(G21:G27)</f>
         <v/>
       </c>
@@ -2409,23 +2412,23 @@
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="39">
+      <c r="C30" s="40">
         <f>IF(C12=0,0,C29/C12)</f>
         <v/>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="40">
         <f>IF(D12=0,0,D29/D12)</f>
         <v/>
       </c>
-      <c r="E30" s="39">
+      <c r="E30" s="40">
         <f>IF(E12=0,0,E29/E12)</f>
         <v/>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="40">
         <f>IF(F12=0,0,F29/F12)</f>
         <v/>
       </c>
-      <c r="G30" s="39">
+      <c r="G30" s="40">
         <f>IF(G12=0,0,G29/G12)</f>
         <v/>
       </c>
@@ -2708,23 +2711,23 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="37">
+      <c r="C4" s="39">
         <f>'損益計算書'!C29</f>
         <v/>
       </c>
-      <c r="D4" s="37">
+      <c r="D4" s="39">
         <f>'損益計算書'!D29</f>
         <v/>
       </c>
-      <c r="E4" s="37">
+      <c r="E4" s="39">
         <f>'損益計算書'!E29</f>
         <v/>
       </c>
-      <c r="F4" s="37">
+      <c r="F4" s="39">
         <f>'損益計算書'!F29</f>
         <v/>
       </c>
-      <c r="G4" s="37">
+      <c r="G4" s="39">
         <f>'損益計算書'!G29</f>
         <v/>
       </c>
@@ -2896,23 +2899,23 @@
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="37">
+      <c r="C11" s="39">
         <f>C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="37">
+      <c r="D11" s="39">
         <f>D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="39">
         <f>E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="39">
         <f>F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="39">
         <f>G9+G10</f>
         <v/>
       </c>
@@ -3097,23 +3100,23 @@
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="37">
+      <c r="C19" s="39">
         <f>C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="39">
         <f>D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="39">
         <f>E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="39">
         <f>F16+F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="39">
         <f>G16+G17+G18</f>
         <v/>
       </c>
@@ -3125,23 +3128,23 @@
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="37">
+      <c r="C21" s="39">
         <f>C14+C15+C19</f>
         <v/>
       </c>
-      <c r="D21" s="37">
+      <c r="D21" s="39">
         <f>D14+D15+D19</f>
         <v/>
       </c>
-      <c r="E21" s="37">
+      <c r="E21" s="39">
         <f>E14+E15+E19</f>
         <v/>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="39">
         <f>F14+F15+F19</f>
         <v/>
       </c>
-      <c r="G21" s="37">
+      <c r="G21" s="39">
         <f>G14+G15+G19</f>
         <v/>
       </c>
@@ -3689,7 +3692,7 @@
           <t>設立（資本金800万）</t>
         </is>
       </c>
-      <c r="C20" s="40" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3714,7 +3717,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="42">
         <f>SUM(D20:H20)</f>
         <v/>
       </c>
@@ -3734,7 +3737,7 @@
           <t>ESOP枠を設計</t>
         </is>
       </c>
-      <c r="C21" s="40" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3759,7 +3762,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="42">
         <f>SUM(D21:H21)</f>
         <v/>
       </c>
@@ -3779,7 +3782,7 @@
           <t>J-KISS 発行（未転換）</t>
         </is>
       </c>
-      <c r="C22" s="40" t="inlineStr">
+      <c r="C22" s="41" t="inlineStr">
         <is>
           <t>1.42億</t>
         </is>
@@ -3804,7 +3807,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="42">
         <f>SUM(D22:H22)</f>
         <v/>
       </c>
@@ -3824,7 +3827,7 @@
           <t>シリーズA ＋ J-KISS転換</t>
         </is>
       </c>
-      <c r="C23" s="40" t="inlineStr">
+      <c r="C23" s="41" t="inlineStr">
         <is>
           <t>3億</t>
         </is>
@@ -3849,7 +3852,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I23" s="41">
+      <c r="I23" s="42">
         <f>SUM(D23:H23)</f>
         <v/>
       </c>
@@ -3869,7 +3872,7 @@
           <t>ESOP補充</t>
         </is>
       </c>
-      <c r="C24" s="40" t="inlineStr">
+      <c r="C24" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3894,7 +3897,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I24" s="41">
+      <c r="I24" s="42">
         <f>SUM(D24:H24)</f>
         <v/>
       </c>
@@ -3914,7 +3917,7 @@
           <t>IPO 公募</t>
         </is>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C25" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3939,7 +3942,7 @@
         <f>$C$12</f>
         <v/>
       </c>
-      <c r="I25" s="41">
+      <c r="I25" s="42">
         <f>SUM(D25:H25)</f>
         <v/>
       </c>
@@ -3959,7 +3962,7 @@
           <t>売出し（既存株主が売る）</t>
         </is>
       </c>
-      <c r="C26" s="40" t="inlineStr">
+      <c r="C26" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3984,7 +3987,7 @@
         <f>H25+$C$13+$C$14</f>
         <v/>
       </c>
-      <c r="I26" s="41">
+      <c r="I26" s="42">
         <f>SUM(D26:H26)</f>
         <v/>
       </c>
@@ -4042,7 +4045,7 @@
           <t>創業者（役員）</t>
         </is>
       </c>
-      <c r="B30" s="39">
+      <c r="B30" s="40">
         <f>D26</f>
         <v/>
       </c>
@@ -4056,7 +4059,7 @@
           <t>× 除外</t>
         </is>
       </c>
-      <c r="E30" s="39" t="n">
+      <c r="E30" s="40" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="7" t="inlineStr">
@@ -4071,7 +4074,7 @@
           <t>ESOP枠</t>
         </is>
       </c>
-      <c r="B31" s="39">
+      <c r="B31" s="40">
         <f>E26</f>
         <v/>
       </c>
@@ -4085,7 +4088,7 @@
           <t>× 除外</t>
         </is>
       </c>
-      <c r="E31" s="39" t="n">
+      <c r="E31" s="40" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
@@ -4100,7 +4103,7 @@
           <t>シード投資家 保有分</t>
         </is>
       </c>
-      <c r="B32" s="39">
+      <c r="B32" s="40">
         <f>F26</f>
         <v/>
       </c>
@@ -4112,7 +4115,7 @@
         <f>IF(B32&lt;0.1,"○ 算入","× 除外")</f>
         <v/>
       </c>
-      <c r="E32" s="39">
+      <c r="E32" s="40">
         <f>IF(B32&lt;0.1,B32,0)</f>
         <v/>
       </c>
@@ -4128,7 +4131,7 @@
           <t>シリーズA 保有分</t>
         </is>
       </c>
-      <c r="B33" s="39">
+      <c r="B33" s="40">
         <f>G26</f>
         <v/>
       </c>
@@ -4140,7 +4143,7 @@
         <f>IF(B33&lt;0.1,"○ 算入","× 除外")</f>
         <v/>
       </c>
-      <c r="E33" s="39">
+      <c r="E33" s="40">
         <f>IF(B33&lt;0.1,B33,0)</f>
         <v/>
       </c>
@@ -4156,7 +4159,7 @@
           <t>公募・売出し</t>
         </is>
       </c>
-      <c r="B34" s="39">
+      <c r="B34" s="40">
         <f>H26</f>
         <v/>
       </c>
@@ -4170,7 +4173,7 @@
           <t>○ 算入</t>
         </is>
       </c>
-      <c r="E34" s="39">
+      <c r="E34" s="40">
         <f>B34</f>
         <v/>
       </c>
@@ -4201,7 +4204,7 @@
         <f>IF(E35&gt;=0.25,"○ 満たす","× 不足")</f>
         <v/>
       </c>
-      <c r="E36" s="42">
+      <c r="E36" s="43">
         <f>E35-0.25</f>
         <v/>
       </c>
@@ -4363,7 +4366,7 @@
           <t>転換後の希薄化</t>
         </is>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="44">
         <f>B8/B6</f>
         <v/>
       </c>
@@ -4511,7 +4514,7 @@
         <f>E13*$B$8</f>
         <v/>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="45">
         <f>F13/$B$5</f>
         <v/>
       </c>
@@ -4548,7 +4551,7 @@
         <f>E14*$B$8</f>
         <v/>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="45">
         <f>F14/$B$5</f>
         <v/>
       </c>
@@ -4581,7 +4584,7 @@
         <f>E15*$B$8</f>
         <v/>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="45">
         <f>F15/$B$5</f>
         <v/>
       </c>
@@ -4658,7 +4661,7 @@
         <f>E19*$B$8</f>
         <v/>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="45">
         <f>F19/$B$5</f>
         <v/>
       </c>
@@ -4689,7 +4692,7 @@
         <f>E20*$B$8</f>
         <v/>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="45">
         <f>F20/$B$5</f>
         <v/>
       </c>
@@ -4959,7 +4962,7 @@
           <t>Runway</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>非開示</t>
         </is>
@@ -4986,7 +4989,7 @@
           <t>Technicolor</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>非開示</t>
         </is>
@@ -5008,16 +5011,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>【当社 5期（2031年）】</t>
         </is>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="47">
         <f>'損益計算書'!$G$12/100</f>
         <v/>
       </c>
-      <c r="C14" s="45" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>①制作＋②ツール＋③C2C</t>
         </is>
@@ -5107,12 +5110,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>── 実測 ──</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr"/>
+      <c r="B4" s="41" t="inlineStr"/>
       <c r="C4" s="16" t="inlineStr"/>
       <c r="D4" s="7" t="inlineStr"/>
     </row>
@@ -5122,7 +5125,7 @@
           <t>国内 映像制作市場</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>4,580億円</t>
         </is>
@@ -5144,7 +5147,7 @@
           <t>インターネット広告制作費</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>4,922億円</t>
         </is>
@@ -5166,7 +5169,7 @@
           <t>法人数</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>295万6,717社</t>
         </is>
@@ -5188,7 +5191,7 @@
           <t>中国 剪辑師 平均月給</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>8,935元</t>
         </is>
@@ -5210,7 +5213,7 @@
           <t>中国 微短劇 直接就業者</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>約69万人</t>
         </is>
@@ -5232,7 +5235,7 @@
           <t>Stripe 決済手数料</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>国内カード3.6%／銀行振込1.5%</t>
         </is>
@@ -5254,7 +5257,7 @@
           <t>S3 Standard 東京</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>1TB/月 ≈ $25</t>
         </is>
@@ -5276,7 +5279,7 @@
           <t>CloudFront 東京</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>$0.085/GB</t>
         </is>
@@ -5298,7 +5301,7 @@
           <t>ベンチマーク各社の売上</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>業界ベンチマーク シート</t>
         </is>
@@ -5320,7 +5323,7 @@
           <t>東証グロース 上場維持基準</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B14" s="41" t="inlineStr">
         <is>
           <t>5年経過後 時価総額100億円</t>
         </is>
@@ -5337,12 +5340,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>── 確認できなかった ──</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr"/>
+      <c r="B15" s="41" t="inlineStr"/>
       <c r="C15" s="16" t="inlineStr"/>
       <c r="D15" s="7" t="inlineStr"/>
     </row>
@@ -5352,7 +5355,7 @@
           <t>スキルシェア市場の映像比率</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>非公表</t>
         </is>
@@ -5369,12 +5372,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="47" t="inlineStr">
+      <c r="A17" s="48" t="inlineStr">
         <is>
           <t>── 松田さんの決定 ──</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr"/>
+      <c r="B17" s="41" t="inlineStr"/>
       <c r="C17" s="16" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr"/>
     </row>
@@ -5384,7 +5387,7 @@
           <t>③ 手数料率</t>
         </is>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>一律30%（クリエイター70%）</t>
         </is>
@@ -5406,7 +5409,7 @@
           <t>③ 送金・為替</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -5428,7 +5431,7 @@
           <t>③ 成約位置</t>
         </is>
       </c>
-      <c r="B20" s="40" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>均等（価格帯の中点）</t>
         </is>
@@ -5450,7 +5453,7 @@
           <t>① クリエイター支払</t>
         </is>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>厚いまま（実効時給3,000〜6,000円）</t>
         </is>
@@ -5472,7 +5475,7 @@
           <t>②-C セルフサーブ</t>
         </is>
       </c>
-      <c r="B22" s="40" t="inlineStr">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>②に置く／用途特化</t>
         </is>
@@ -5489,12 +5492,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="47" t="inlineStr">
+      <c r="A23" s="48" t="inlineStr">
         <is>
           <t>── ★私が置いた値 ──</t>
         </is>
       </c>
-      <c r="B23" s="40" t="inlineStr"/>
+      <c r="B23" s="41" t="inlineStr"/>
       <c r="C23" s="16" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr"/>
     </row>
@@ -5504,7 +5507,7 @@
           <t>AX倍率</t>
         </is>
       </c>
-      <c r="B24" s="40" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>1.0 → 4.0倍</t>
         </is>
@@ -5526,7 +5529,7 @@
           <t>① 商品の値引率</t>
         </is>
       </c>
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B25" s="41" t="inlineStr">
         <is>
           <t>一律50%</t>
         </is>
@@ -5548,7 +5551,7 @@
           <t>① 難度係数</t>
         </is>
       </c>
-      <c r="B26" s="40" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>3.0 / 1.8 / 1.0 / 0.8</t>
         </is>
@@ -5570,7 +5573,7 @@
           <t>① 商品構成比</t>
         </is>
       </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>年を追って上位帯へシフト</t>
         </is>
@@ -5592,7 +5595,7 @@
           <t>① 営業の担当社数・リピート</t>
         </is>
       </c>
-      <c r="B28" s="40" t="inlineStr">
+      <c r="B28" s="41" t="inlineStr">
         <is>
           <t>40社／年6本</t>
         </is>
@@ -5614,7 +5617,7 @@
           <t>② SKU単価・席数・Ent比率</t>
         </is>
       </c>
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="41" t="inlineStr">
         <is>
           <t>商品マスタ② 参照</t>
         </is>
@@ -5636,7 +5639,7 @@
           <t>③ 工数・上限価格・件数</t>
         </is>
       </c>
-      <c r="B30" s="40" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>商品マスタ③ 参照</t>
         </is>
@@ -5658,7 +5661,7 @@
           <t>③ システム原価の内訳</t>
         </is>
       </c>
-      <c r="B31" s="40" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>尺・保管期間・トークン数</t>
         </is>
@@ -5680,7 +5683,7 @@
           <t>希薄化係数</t>
         </is>
       </c>
-      <c r="B32" s="40" t="inlineStr">
+      <c r="B32" s="41" t="inlineStr">
         <is>
           <t>資本構成の推移 参照</t>
         </is>
@@ -5697,12 +5700,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="47" t="inlineStr">
+      <c r="A33" s="48" t="inlineStr">
         <is>
           <t>── 未確定 ──</t>
         </is>
       </c>
-      <c r="B33" s="40" t="inlineStr"/>
+      <c r="B33" s="41" t="inlineStr"/>
       <c r="C33" s="16" t="inlineStr"/>
       <c r="D33" s="7" t="inlineStr"/>
     </row>
@@ -5712,7 +5715,7 @@
           <t>中国の映像制作パートナー</t>
         </is>
       </c>
-      <c r="B34" s="40" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>社名 ［記入予定］</t>
         </is>
@@ -5734,7 +5737,7 @@
           <t>パートナーの取り分</t>
         </is>
       </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="B35" s="41" t="inlineStr">
         <is>
           <t>30%側か70%側か</t>
         </is>
@@ -5756,7 +5759,7 @@
           <t>業務委託の契約設計</t>
         </is>
       </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="41" t="inlineStr">
         <is>
           <t>─</t>
         </is>
@@ -5829,12 +5832,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5852,7 +5855,7 @@
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr"/>
-      <c r="B5" s="49" t="inlineStr"/>
+      <c r="B5" s="50" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>市場規模の次に「業界の売上」を新設</t>
@@ -5865,12 +5868,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5888,7 +5891,7 @@
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr"/>
-      <c r="B7" s="49" t="inlineStr"/>
+      <c r="B7" s="50" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>① 単価を「企業の現行支払×50%」に。本数は営業体制から</t>
@@ -5902,7 +5905,7 @@
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr"/>
-      <c r="B8" s="49" t="inlineStr"/>
+      <c r="B8" s="50" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>② 5SKU・法人2階建て・②-Cセルフサーブを新設</t>
@@ -5916,7 +5919,7 @@
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr"/>
-      <c r="B9" s="49" t="inlineStr"/>
+      <c r="B9" s="50" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>③ 14商品。下限はクリエイターの留保価格、上限は日本の支払意思</t>
@@ -5929,12 +5932,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5952,7 +5955,7 @@
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr"/>
-      <c r="B11" s="49" t="inlineStr"/>
+      <c r="B11" s="50" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
           <t>③ 手数料を一律30%に。30%から決済・送金・システム原価を引く</t>
@@ -5966,7 +5969,7 @@
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr"/>
-      <c r="B12" s="49" t="inlineStr"/>
+      <c r="B12" s="50" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>③ システム原価を商品別に積み上げ（120円→53円）</t>
@@ -5980,7 +5983,7 @@
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr"/>
-      <c r="B13" s="49" t="inlineStr"/>
+      <c r="B13" s="50" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>② ACVとARRを分離。①③のARRはゼロと明示</t>
@@ -5994,7 +5997,7 @@
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr"/>
-      <c r="B14" s="49" t="inlineStr"/>
+      <c r="B14" s="50" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>エンジニアを社員40名 → PM4名＋ベトナム委託19名</t>
@@ -6008,7 +6011,7 @@
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr"/>
-      <c r="B15" s="49" t="inlineStr"/>
+      <c r="B15" s="50" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>エンジニアにもAX倍率（5期2.2倍）</t>
@@ -6022,7 +6025,7 @@
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr"/>
-      <c r="B16" s="49" t="inlineStr"/>
+      <c r="B16" s="50" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>中国・東欧・ロシアを委託先から外す</t>
@@ -6036,7 +6039,7 @@
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr"/>
-      <c r="B17" s="49" t="inlineStr"/>
+      <c r="B17" s="50" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
           <t>管理・コーポレートを6名→3名</t>
@@ -6049,7 +6052,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>⚠ 1.4 → 1.5 は構造の作り直し、1.5 → 1.6 は前提を実勢データで詰めたもの。5期の売上は 88.1億 → 108.0億、社員は 61名 → 22名。数字が良くなった分だけ、前提の説明責任が重くなっている。</t>
         </is>
@@ -10648,7 +10651,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>下限はクリエイターの留保価格（標準工数×時給÷(1−手数料)）。上限は日本の発注者の支払意思。工数は旧maxを標準に置き直した（ミニマムの見立てが甘かったため）。★上限・工数・件数は提案値。</t>
+          <t>価格は上限を採用（松田さんの決定）。上限＝日本の発注者の支払意思。下限はクリエイターの留保価格で、下回ると供給が付かないという床。中点は参考。</t>
         </is>
       </c>
     </row>
@@ -10680,12 +10683,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>上限（需要）</t>
+          <t>上限＝採用価格</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>中点</t>
+          <t>参考 中点</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -10730,10 +10733,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D5/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="35">
         <f>(E5+F5)/2</f>
         <v/>
       </c>
@@ -10745,7 +10748,7 @@
         <v/>
       </c>
       <c r="J5" s="29">
-        <f>G5*H5/1000000</f>
+        <f>F5*H5/1000000</f>
         <v/>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -10775,10 +10778,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D6/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="35">
         <f>(E6+F6)/2</f>
         <v/>
       </c>
@@ -10790,7 +10793,7 @@
         <v/>
       </c>
       <c r="J6" s="29">
-        <f>G6*H6/1000000</f>
+        <f>F6*H6/1000000</f>
         <v/>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -10820,10 +10823,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D7/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="35">
         <f>(E7+F7)/2</f>
         <v/>
       </c>
@@ -10835,7 +10838,7 @@
         <v/>
       </c>
       <c r="J7" s="29">
-        <f>G7*H7/1000000</f>
+        <f>F7*H7/1000000</f>
         <v/>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -10865,10 +10868,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D8/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="35">
         <f>(E8+F8)/2</f>
         <v/>
       </c>
@@ -10880,7 +10883,7 @@
         <v/>
       </c>
       <c r="J8" s="29">
-        <f>G8*H8/1000000</f>
+        <f>F8*H8/1000000</f>
         <v/>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -10910,10 +10913,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D9/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="35">
         <f>(E9+F9)/2</f>
         <v/>
       </c>
@@ -10925,7 +10928,7 @@
         <v/>
       </c>
       <c r="J9" s="29">
-        <f>G9*H9/1000000</f>
+        <f>F9*H9/1000000</f>
         <v/>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -10955,10 +10958,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D10/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="6" t="n">
         <v>80000</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="35">
         <f>(E10+F10)/2</f>
         <v/>
       </c>
@@ -10970,7 +10973,7 @@
         <v/>
       </c>
       <c r="J10" s="29">
-        <f>G10*H10/1000000</f>
+        <f>F10*H10/1000000</f>
         <v/>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -11000,10 +11003,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D11/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="6" t="n">
         <v>120000</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="35">
         <f>(E11+F11)/2</f>
         <v/>
       </c>
@@ -11015,7 +11018,7 @@
         <v/>
       </c>
       <c r="J11" s="29">
-        <f>G11*H11/1000000</f>
+        <f>F11*H11/1000000</f>
         <v/>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -11045,10 +11048,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D12/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="6" t="n">
         <v>180000</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="35">
         <f>(E12+F12)/2</f>
         <v/>
       </c>
@@ -11060,7 +11063,7 @@
         <v/>
       </c>
       <c r="J12" s="29">
-        <f>G12*H12/1000000</f>
+        <f>F12*H12/1000000</f>
         <v/>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -11090,10 +11093,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D13/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="6" t="n">
         <v>150000</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="35">
         <f>(E13+F13)/2</f>
         <v/>
       </c>
@@ -11105,7 +11108,7 @@
         <v/>
       </c>
       <c r="J13" s="29">
-        <f>G13*H13/1000000</f>
+        <f>F13*H13/1000000</f>
         <v/>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -11135,10 +11138,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D14/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="35">
         <f>(E14+F14)/2</f>
         <v/>
       </c>
@@ -11150,7 +11153,7 @@
         <v/>
       </c>
       <c r="J14" s="29">
-        <f>G14*H14/1000000</f>
+        <f>F14*H14/1000000</f>
         <v/>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -11180,10 +11183,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D15/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="6" t="n">
         <v>80000</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="35">
         <f>(E15+F15)/2</f>
         <v/>
       </c>
@@ -11195,7 +11198,7 @@
         <v/>
       </c>
       <c r="J15" s="29">
-        <f>G15*H15/1000000</f>
+        <f>F15*H15/1000000</f>
         <v/>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -11225,10 +11228,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D16/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="6" t="n">
         <v>120000</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="35">
         <f>(E16+F16)/2</f>
         <v/>
       </c>
@@ -11240,7 +11243,7 @@
         <v/>
       </c>
       <c r="J16" s="29">
-        <f>G16*H16/1000000</f>
+        <f>F16*H16/1000000</f>
         <v/>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -11270,10 +11273,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D17/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="6" t="n">
         <v>150000</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="35">
         <f>(E17+F17)/2</f>
         <v/>
       </c>
@@ -11285,7 +11288,7 @@
         <v/>
       </c>
       <c r="J17" s="29">
-        <f>G17*H17/1000000</f>
+        <f>F17*H17/1000000</f>
         <v/>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -11315,10 +11318,10 @@
         <f>ROUNDUP('クリエイター経済'!$B$10*D18/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="6" t="n">
         <v>1000000</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="35">
         <f>(E18+F18)/2</f>
         <v/>
       </c>
@@ -11330,7 +11333,7 @@
         <v/>
       </c>
       <c r="J18" s="29">
-        <f>G18*H18/1000000</f>
+        <f>F18*H18/1000000</f>
         <v/>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -11443,7 +11446,7 @@
           <t>手数料率</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n">
+      <c r="B26" s="36" t="n">
         <v>0.3</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -11458,7 +11461,7 @@
           <t>決済手数料率</t>
         </is>
       </c>
-      <c r="B27" s="35" t="n">
+      <c r="B27" s="36" t="n">
         <v>0.0318</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -11473,7 +11476,7 @@
           <t>送金・為替</t>
         </is>
       </c>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="36" t="n">
         <v>0.03</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -11865,10 +11868,38 @@
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="36" t="inlineStr">
-        <is>
-          <t>成約が価格帯のどこに落ちるかで③は3倍動く。ここは中点（均等）を採用している（松田さん決定）。下限寄りに寄ると小さくなる。</t>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>年間工数（時間）</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="23">
+        <f>$I$20*C32*(1-C35)+$I$21*C33+$I$22*C34</f>
+        <v/>
+      </c>
+      <c r="D44" s="23">
+        <f>$I$20*D32*(1-D35)+$I$21*D33+$I$22*D34</f>
+        <v/>
+      </c>
+      <c r="E44" s="23">
+        <f>$I$20*E32*(1-E35)+$I$21*E33+$I$22*E34</f>
+        <v/>
+      </c>
+      <c r="F44" s="23">
+        <f>$I$20*F32*(1-F35)+$I$21*F33+$I$22*F34</f>
+        <v/>
+      </c>
+      <c r="G44" s="23">
+        <f>$I$20*G32*(1-G35)+$I$21*G33+$I$22*G34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t>⚠ 全商品が上限で成約する前提。下限（クリエイターの留保価格）との差がそのまま利幅になる。供給が厚いほど競争で下限側に寄るのが市場の常なので、ここは最も強気の置き方。中点なら③のGMVは約57%、全部が下限なら約5%になる。</t>
         </is>
       </c>
     </row>
@@ -12418,16 +12449,64 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>中国クリエイター（稼働・人）</t>
+        </is>
+      </c>
+      <c r="C17" s="8">
+        <f>('商品マスタ③'!C44+'商品マスタ①'!I15*1000000/4000)/1800</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>('商品マスタ③'!D44+'商品マスタ①'!J15*1000000/4000)/1800</f>
+        <v/>
+      </c>
+      <c r="E17" s="8">
+        <f>('商品マスタ③'!E44+'商品マスタ①'!K15*1000000/4000)/1800</f>
+        <v/>
+      </c>
+      <c r="F17" s="8">
+        <f>('商品マスタ③'!F44+'商品マスタ①'!L15*1000000/4000)/1800</f>
+        <v/>
+      </c>
+      <c r="G17" s="8">
+        <f>('商品マスタ③'!G44+'商品マスタ①'!M15*1000000/4000)/1800</f>
+        <v/>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>（③の年間工数 ＋ ①のクリエイター支払÷実効時給4,000円）÷ 年1,800時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>中国クリエイター（登録・人）</t>
         </is>
       </c>
-      <c r="G17" s="37">
-        <f>'クリエイター経済'!B18</f>
-        <v/>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>クリエイター経済シート。①③の合計</t>
+      <c r="C18" s="6">
+        <f>C17*2.5</f>
+        <v/>
+      </c>
+      <c r="D18" s="6">
+        <f>D17*2.5</f>
+        <v/>
+      </c>
+      <c r="E18" s="6">
+        <f>E17*2.5</f>
+        <v/>
+      </c>
+      <c r="F18" s="6">
+        <f>F17*2.5</f>
+        <v/>
+      </c>
+      <c r="G18" s="6">
+        <f>G17*2.5</f>
+        <v/>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>稼働の2.5倍★。全員が常時稼働はしない</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12686,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
         <is>
           <t>⚠ 安い順は ミャンマー(40)＜インド(45)＜フィリピン(47.5)＜ベトナム(50)＜中国(71.7)＜東欧(104)。ロシア・ベラルーシは外為法の役務取引規制（2022/3/18〜）で対象外。単価の問題ではない。</t>
         </is>
@@ -12821,7 +12900,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>⚠ 管理・コーポレート3名は、5期に上場会社として内部統制報告制度の対象になる規模には薄い。取引処理はBPOに出す前提だが、内部統制の設計・運用・評価は社員の仕事。監査法人と主幹事に早期に当てること。★確認事項</t>
         </is>

--- a/事業計画_Ver1.6.xlsx
+++ b/事業計画_Ver1.6.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -235,6 +235,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -2174,23 +2177,23 @@
       </c>
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="8">
-        <f>'人員と人件費'!C38</f>
+        <f>'人員と人件費'!C42</f>
         <v/>
       </c>
       <c r="D22" s="8">
-        <f>'人員と人件費'!D38</f>
+        <f>'人員と人件費'!D42</f>
         <v/>
       </c>
       <c r="E22" s="8">
-        <f>'人員と人件費'!E38</f>
+        <f>'人員と人件費'!E42</f>
         <v/>
       </c>
       <c r="F22" s="8">
-        <f>'人員と人件費'!F38</f>
+        <f>'人員と人件費'!F42</f>
         <v/>
       </c>
       <c r="G22" s="8">
-        <f>'人員と人件費'!G38</f>
+        <f>'人員と人件費'!G42</f>
         <v/>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2356,23 +2359,23 @@
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="39">
+      <c r="C28" s="40">
         <f>SUM(C21:C27)</f>
         <v/>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="40">
         <f>SUM(D21:D27)</f>
         <v/>
       </c>
-      <c r="E28" s="39">
+      <c r="E28" s="40">
         <f>SUM(E21:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="39">
+      <c r="F28" s="40">
         <f>SUM(F21:F27)</f>
         <v/>
       </c>
-      <c r="G28" s="39">
+      <c r="G28" s="40">
         <f>SUM(G21:G27)</f>
         <v/>
       </c>
@@ -2412,23 +2415,23 @@
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="40">
+      <c r="C30" s="41">
         <f>IF(C12=0,0,C29/C12)</f>
         <v/>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="41">
         <f>IF(D12=0,0,D29/D12)</f>
         <v/>
       </c>
-      <c r="E30" s="40">
+      <c r="E30" s="41">
         <f>IF(E12=0,0,E29/E12)</f>
         <v/>
       </c>
-      <c r="F30" s="40">
+      <c r="F30" s="41">
         <f>IF(F12=0,0,F29/F12)</f>
         <v/>
       </c>
-      <c r="G30" s="40">
+      <c r="G30" s="41">
         <f>IF(G12=0,0,G29/G12)</f>
         <v/>
       </c>
@@ -2711,23 +2714,23 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="39">
+      <c r="C4" s="40">
         <f>'損益計算書'!C29</f>
         <v/>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="40">
         <f>'損益計算書'!D29</f>
         <v/>
       </c>
-      <c r="E4" s="39">
+      <c r="E4" s="40">
         <f>'損益計算書'!E29</f>
         <v/>
       </c>
-      <c r="F4" s="39">
+      <c r="F4" s="40">
         <f>'損益計算書'!F29</f>
         <v/>
       </c>
-      <c r="G4" s="39">
+      <c r="G4" s="40">
         <f>'損益計算書'!G29</f>
         <v/>
       </c>
@@ -2899,23 +2902,23 @@
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="39">
+      <c r="C11" s="40">
         <f>C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="40">
         <f>D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="40">
         <f>E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="40">
         <f>F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="40">
         <f>G9+G10</f>
         <v/>
       </c>
@@ -3100,23 +3103,23 @@
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="39">
+      <c r="C19" s="40">
         <f>C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="40">
         <f>D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="40">
         <f>E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="40">
         <f>F16+F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="39">
+      <c r="G19" s="40">
         <f>G16+G17+G18</f>
         <v/>
       </c>
@@ -3128,23 +3131,23 @@
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="39">
+      <c r="C21" s="40">
         <f>C14+C15+C19</f>
         <v/>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="40">
         <f>D14+D15+D19</f>
         <v/>
       </c>
-      <c r="E21" s="39">
+      <c r="E21" s="40">
         <f>E14+E15+E19</f>
         <v/>
       </c>
-      <c r="F21" s="39">
+      <c r="F21" s="40">
         <f>F14+F15+F19</f>
         <v/>
       </c>
-      <c r="G21" s="39">
+      <c r="G21" s="40">
         <f>G14+G15+G19</f>
         <v/>
       </c>
@@ -3596,7 +3599,7 @@
           <t>転換時のシード持分</t>
         </is>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="39">
         <f>C7/C6</f>
         <v/>
       </c>
@@ -3612,7 +3615,7 @@
           <t>シリーズA の持分</t>
         </is>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="39">
         <f>C10/C9</f>
         <v/>
       </c>
@@ -3692,7 +3695,7 @@
           <t>設立（資本金800万）</t>
         </is>
       </c>
-      <c r="C20" s="41" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3717,7 +3720,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I20" s="42">
+      <c r="I20" s="43">
         <f>SUM(D20:H20)</f>
         <v/>
       </c>
@@ -3737,7 +3740,7 @@
           <t>ESOP枠を設計</t>
         </is>
       </c>
-      <c r="C21" s="41" t="inlineStr">
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3762,7 +3765,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I21" s="42">
+      <c r="I21" s="43">
         <f>SUM(D21:H21)</f>
         <v/>
       </c>
@@ -3782,7 +3785,7 @@
           <t>J-KISS 発行（未転換）</t>
         </is>
       </c>
-      <c r="C22" s="41" t="inlineStr">
+      <c r="C22" s="42" t="inlineStr">
         <is>
           <t>1.42億</t>
         </is>
@@ -3807,7 +3810,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I22" s="42">
+      <c r="I22" s="43">
         <f>SUM(D22:H22)</f>
         <v/>
       </c>
@@ -3827,7 +3830,7 @@
           <t>シリーズA ＋ J-KISS転換</t>
         </is>
       </c>
-      <c r="C23" s="41" t="inlineStr">
+      <c r="C23" s="42" t="inlineStr">
         <is>
           <t>3億</t>
         </is>
@@ -3852,7 +3855,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I23" s="42">
+      <c r="I23" s="43">
         <f>SUM(D23:H23)</f>
         <v/>
       </c>
@@ -3872,7 +3875,7 @@
           <t>ESOP補充</t>
         </is>
       </c>
-      <c r="C24" s="41" t="inlineStr">
+      <c r="C24" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3897,7 +3900,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I24" s="42">
+      <c r="I24" s="43">
         <f>SUM(D24:H24)</f>
         <v/>
       </c>
@@ -3917,7 +3920,7 @@
           <t>IPO 公募</t>
         </is>
       </c>
-      <c r="C25" s="41" t="inlineStr">
+      <c r="C25" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3942,7 +3945,7 @@
         <f>$C$12</f>
         <v/>
       </c>
-      <c r="I25" s="42">
+      <c r="I25" s="43">
         <f>SUM(D25:H25)</f>
         <v/>
       </c>
@@ -3962,7 +3965,7 @@
           <t>売出し（既存株主が売る）</t>
         </is>
       </c>
-      <c r="C26" s="41" t="inlineStr">
+      <c r="C26" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3987,7 +3990,7 @@
         <f>H25+$C$13+$C$14</f>
         <v/>
       </c>
-      <c r="I26" s="42">
+      <c r="I26" s="43">
         <f>SUM(D26:H26)</f>
         <v/>
       </c>
@@ -4045,7 +4048,7 @@
           <t>創業者（役員）</t>
         </is>
       </c>
-      <c r="B30" s="40">
+      <c r="B30" s="41">
         <f>D26</f>
         <v/>
       </c>
@@ -4059,7 +4062,7 @@
           <t>× 除外</t>
         </is>
       </c>
-      <c r="E30" s="40" t="n">
+      <c r="E30" s="41" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="7" t="inlineStr">
@@ -4074,7 +4077,7 @@
           <t>ESOP枠</t>
         </is>
       </c>
-      <c r="B31" s="40">
+      <c r="B31" s="41">
         <f>E26</f>
         <v/>
       </c>
@@ -4088,7 +4091,7 @@
           <t>× 除外</t>
         </is>
       </c>
-      <c r="E31" s="40" t="n">
+      <c r="E31" s="41" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
@@ -4103,7 +4106,7 @@
           <t>シード投資家 保有分</t>
         </is>
       </c>
-      <c r="B32" s="40">
+      <c r="B32" s="41">
         <f>F26</f>
         <v/>
       </c>
@@ -4115,7 +4118,7 @@
         <f>IF(B32&lt;0.1,"○ 算入","× 除外")</f>
         <v/>
       </c>
-      <c r="E32" s="40">
+      <c r="E32" s="41">
         <f>IF(B32&lt;0.1,B32,0)</f>
         <v/>
       </c>
@@ -4131,7 +4134,7 @@
           <t>シリーズA 保有分</t>
         </is>
       </c>
-      <c r="B33" s="40">
+      <c r="B33" s="41">
         <f>G26</f>
         <v/>
       </c>
@@ -4143,7 +4146,7 @@
         <f>IF(B33&lt;0.1,"○ 算入","× 除外")</f>
         <v/>
       </c>
-      <c r="E33" s="40">
+      <c r="E33" s="41">
         <f>IF(B33&lt;0.1,B33,0)</f>
         <v/>
       </c>
@@ -4159,7 +4162,7 @@
           <t>公募・売出し</t>
         </is>
       </c>
-      <c r="B34" s="40">
+      <c r="B34" s="41">
         <f>H26</f>
         <v/>
       </c>
@@ -4173,7 +4176,7 @@
           <t>○ 算入</t>
         </is>
       </c>
-      <c r="E34" s="40">
+      <c r="E34" s="41">
         <f>B34</f>
         <v/>
       </c>
@@ -4204,7 +4207,7 @@
         <f>IF(E35&gt;=0.25,"○ 満たす","× 不足")</f>
         <v/>
       </c>
-      <c r="E36" s="43">
+      <c r="E36" s="44">
         <f>E35-0.25</f>
         <v/>
       </c>
@@ -4340,7 +4343,7 @@
           <t>転換時のシード持分</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="39">
         <f>'資本構成の推移'!C15</f>
         <v/>
       </c>
@@ -4366,7 +4369,7 @@
           <t>転換後の希薄化</t>
         </is>
       </c>
-      <c r="B7" s="44">
+      <c r="B7" s="45">
         <f>B8/B6</f>
         <v/>
       </c>
@@ -4392,7 +4395,7 @@
           <t>上場後のシード持分</t>
         </is>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="39">
         <f>'資本構成の推移'!F25</f>
         <v/>
       </c>
@@ -4514,7 +4517,7 @@
         <f>E13*$B$8</f>
         <v/>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="46">
         <f>F13/$B$5</f>
         <v/>
       </c>
@@ -4551,7 +4554,7 @@
         <f>E14*$B$8</f>
         <v/>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="46">
         <f>F14/$B$5</f>
         <v/>
       </c>
@@ -4584,7 +4587,7 @@
         <f>E15*$B$8</f>
         <v/>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="46">
         <f>F15/$B$5</f>
         <v/>
       </c>
@@ -4661,7 +4664,7 @@
         <f>E19*$B$8</f>
         <v/>
       </c>
-      <c r="G19" s="45">
+      <c r="G19" s="46">
         <f>F19/$B$5</f>
         <v/>
       </c>
@@ -4692,7 +4695,7 @@
         <f>E20*$B$8</f>
         <v/>
       </c>
-      <c r="G20" s="45">
+      <c r="G20" s="46">
         <f>F20/$B$5</f>
         <v/>
       </c>
@@ -4962,7 +4965,7 @@
           <t>Runway</t>
         </is>
       </c>
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>非開示</t>
         </is>
@@ -4989,7 +4992,7 @@
           <t>Technicolor</t>
         </is>
       </c>
-      <c r="B13" s="41" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>非開示</t>
         </is>
@@ -5011,16 +5014,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="46" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>【当社 5期（2031年）】</t>
         </is>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="48">
         <f>'損益計算書'!$G$12/100</f>
         <v/>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t>①制作＋②ツール＋③C2C</t>
         </is>
@@ -5110,12 +5113,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>── 実測 ──</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr"/>
+      <c r="B4" s="42" t="inlineStr"/>
       <c r="C4" s="16" t="inlineStr"/>
       <c r="D4" s="7" t="inlineStr"/>
     </row>
@@ -5125,7 +5128,7 @@
           <t>国内 映像制作市場</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>4,580億円</t>
         </is>
@@ -5147,7 +5150,7 @@
           <t>インターネット広告制作費</t>
         </is>
       </c>
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>4,922億円</t>
         </is>
@@ -5169,7 +5172,7 @@
           <t>法人数</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>295万6,717社</t>
         </is>
@@ -5191,7 +5194,7 @@
           <t>中国 剪辑師 平均月給</t>
         </is>
       </c>
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>8,935元</t>
         </is>
@@ -5213,7 +5216,7 @@
           <t>中国 微短劇 直接就業者</t>
         </is>
       </c>
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>約69万人</t>
         </is>
@@ -5235,7 +5238,7 @@
           <t>Stripe 決済手数料</t>
         </is>
       </c>
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>国内カード3.6%／銀行振込1.5%</t>
         </is>
@@ -5257,7 +5260,7 @@
           <t>S3 Standard 東京</t>
         </is>
       </c>
-      <c r="B11" s="41" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>1TB/月 ≈ $25</t>
         </is>
@@ -5279,7 +5282,7 @@
           <t>CloudFront 東京</t>
         </is>
       </c>
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>$0.085/GB</t>
         </is>
@@ -5301,7 +5304,7 @@
           <t>ベンチマーク各社の売上</t>
         </is>
       </c>
-      <c r="B13" s="41" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>業界ベンチマーク シート</t>
         </is>
@@ -5323,7 +5326,7 @@
           <t>東証グロース 上場維持基準</t>
         </is>
       </c>
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>5年経過後 時価総額100億円</t>
         </is>
@@ -5340,12 +5343,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>── 確認できなかった ──</t>
         </is>
       </c>
-      <c r="B15" s="41" t="inlineStr"/>
+      <c r="B15" s="42" t="inlineStr"/>
       <c r="C15" s="16" t="inlineStr"/>
       <c r="D15" s="7" t="inlineStr"/>
     </row>
@@ -5355,7 +5358,7 @@
           <t>スキルシェア市場の映像比率</t>
         </is>
       </c>
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>非公表</t>
         </is>
@@ -5372,12 +5375,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>── 松田さんの決定 ──</t>
         </is>
       </c>
-      <c r="B17" s="41" t="inlineStr"/>
+      <c r="B17" s="42" t="inlineStr"/>
       <c r="C17" s="16" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr"/>
     </row>
@@ -5387,7 +5390,7 @@
           <t>③ 手数料率</t>
         </is>
       </c>
-      <c r="B18" s="41" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>一律30%（クリエイター70%）</t>
         </is>
@@ -5409,7 +5412,7 @@
           <t>③ 送金・為替</t>
         </is>
       </c>
-      <c r="B19" s="41" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -5431,7 +5434,7 @@
           <t>③ 成約位置</t>
         </is>
       </c>
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B20" s="42" t="inlineStr">
         <is>
           <t>均等（価格帯の中点）</t>
         </is>
@@ -5453,7 +5456,7 @@
           <t>① クリエイター支払</t>
         </is>
       </c>
-      <c r="B21" s="41" t="inlineStr">
+      <c r="B21" s="42" t="inlineStr">
         <is>
           <t>厚いまま（実効時給3,000〜6,000円）</t>
         </is>
@@ -5475,7 +5478,7 @@
           <t>②-C セルフサーブ</t>
         </is>
       </c>
-      <c r="B22" s="41" t="inlineStr">
+      <c r="B22" s="42" t="inlineStr">
         <is>
           <t>②に置く／用途特化</t>
         </is>
@@ -5492,12 +5495,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="49" t="inlineStr">
         <is>
           <t>── ★私が置いた値 ──</t>
         </is>
       </c>
-      <c r="B23" s="41" t="inlineStr"/>
+      <c r="B23" s="42" t="inlineStr"/>
       <c r="C23" s="16" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr"/>
     </row>
@@ -5507,7 +5510,7 @@
           <t>AX倍率</t>
         </is>
       </c>
-      <c r="B24" s="41" t="inlineStr">
+      <c r="B24" s="42" t="inlineStr">
         <is>
           <t>1.0 → 4.0倍</t>
         </is>
@@ -5529,7 +5532,7 @@
           <t>① 商品の値引率</t>
         </is>
       </c>
-      <c r="B25" s="41" t="inlineStr">
+      <c r="B25" s="42" t="inlineStr">
         <is>
           <t>一律50%</t>
         </is>
@@ -5551,7 +5554,7 @@
           <t>① 難度係数</t>
         </is>
       </c>
-      <c r="B26" s="41" t="inlineStr">
+      <c r="B26" s="42" t="inlineStr">
         <is>
           <t>3.0 / 1.8 / 1.0 / 0.8</t>
         </is>
@@ -5573,7 +5576,7 @@
           <t>① 商品構成比</t>
         </is>
       </c>
-      <c r="B27" s="41" t="inlineStr">
+      <c r="B27" s="42" t="inlineStr">
         <is>
           <t>年を追って上位帯へシフト</t>
         </is>
@@ -5595,7 +5598,7 @@
           <t>① 営業の担当社数・リピート</t>
         </is>
       </c>
-      <c r="B28" s="41" t="inlineStr">
+      <c r="B28" s="42" t="inlineStr">
         <is>
           <t>40社／年6本</t>
         </is>
@@ -5617,7 +5620,7 @@
           <t>② SKU単価・席数・Ent比率</t>
         </is>
       </c>
-      <c r="B29" s="41" t="inlineStr">
+      <c r="B29" s="42" t="inlineStr">
         <is>
           <t>商品マスタ② 参照</t>
         </is>
@@ -5639,7 +5642,7 @@
           <t>③ 工数・上限価格・件数</t>
         </is>
       </c>
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B30" s="42" t="inlineStr">
         <is>
           <t>商品マスタ③ 参照</t>
         </is>
@@ -5661,7 +5664,7 @@
           <t>③ システム原価の内訳</t>
         </is>
       </c>
-      <c r="B31" s="41" t="inlineStr">
+      <c r="B31" s="42" t="inlineStr">
         <is>
           <t>尺・保管期間・トークン数</t>
         </is>
@@ -5683,7 +5686,7 @@
           <t>希薄化係数</t>
         </is>
       </c>
-      <c r="B32" s="41" t="inlineStr">
+      <c r="B32" s="42" t="inlineStr">
         <is>
           <t>資本構成の推移 参照</t>
         </is>
@@ -5700,12 +5703,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="inlineStr">
+      <c r="A33" s="49" t="inlineStr">
         <is>
           <t>── 未確定 ──</t>
         </is>
       </c>
-      <c r="B33" s="41" t="inlineStr"/>
+      <c r="B33" s="42" t="inlineStr"/>
       <c r="C33" s="16" t="inlineStr"/>
       <c r="D33" s="7" t="inlineStr"/>
     </row>
@@ -5715,7 +5718,7 @@
           <t>中国の映像制作パートナー</t>
         </is>
       </c>
-      <c r="B34" s="41" t="inlineStr">
+      <c r="B34" s="42" t="inlineStr">
         <is>
           <t>社名 ［記入予定］</t>
         </is>
@@ -5737,7 +5740,7 @@
           <t>パートナーの取り分</t>
         </is>
       </c>
-      <c r="B35" s="41" t="inlineStr">
+      <c r="B35" s="42" t="inlineStr">
         <is>
           <t>30%側か70%側か</t>
         </is>
@@ -5759,7 +5762,7 @@
           <t>業務委託の契約設計</t>
         </is>
       </c>
-      <c r="B36" s="41" t="inlineStr">
+      <c r="B36" s="42" t="inlineStr">
         <is>
           <t>─</t>
         </is>
@@ -5786,7 +5789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5832,12 +5835,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5855,7 +5858,7 @@
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr"/>
-      <c r="B5" s="50" t="inlineStr"/>
+      <c r="B5" s="51" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>市場規模の次に「業界の売上」を新設</t>
@@ -5868,12 +5871,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B6" s="50" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5891,7 +5894,7 @@
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr"/>
-      <c r="B7" s="50" t="inlineStr"/>
+      <c r="B7" s="51" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>① 単価を「企業の現行支払×50%」に。本数は営業体制から</t>
@@ -5905,7 +5908,7 @@
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr"/>
-      <c r="B8" s="50" t="inlineStr"/>
+      <c r="B8" s="51" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>② 5SKU・法人2階建て・②-Cセルフサーブを新設</t>
@@ -5919,7 +5922,7 @@
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr"/>
-      <c r="B9" s="50" t="inlineStr"/>
+      <c r="B9" s="51" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>③ 14商品。下限はクリエイターの留保価格、上限は日本の支払意思</t>
@@ -5932,12 +5935,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="B10" s="50" t="inlineStr">
+      <c r="B10" s="51" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5955,7 +5958,7 @@
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr"/>
-      <c r="B11" s="50" t="inlineStr"/>
+      <c r="B11" s="51" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
           <t>③ 手数料を一律30%に。30%から決済・送金・システム原価を引く</t>
@@ -5969,7 +5972,7 @@
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr"/>
-      <c r="B12" s="50" t="inlineStr"/>
+      <c r="B12" s="51" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>③ システム原価を商品別に積み上げ（120円→53円）</t>
@@ -5983,7 +5986,7 @@
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr"/>
-      <c r="B13" s="50" t="inlineStr"/>
+      <c r="B13" s="51" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>② ACVとARRを分離。①③のARRはゼロと明示</t>
@@ -5997,7 +6000,7 @@
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr"/>
-      <c r="B14" s="50" t="inlineStr"/>
+      <c r="B14" s="51" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>エンジニアを社員40名 → PM4名＋ベトナム委託19名</t>
@@ -6011,7 +6014,7 @@
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr"/>
-      <c r="B15" s="50" t="inlineStr"/>
+      <c r="B15" s="51" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>エンジニアにもAX倍率（5期2.2倍）</t>
@@ -6025,7 +6028,7 @@
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr"/>
-      <c r="B16" s="50" t="inlineStr"/>
+      <c r="B16" s="51" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>中国・東欧・ロシアを委託先から外す</t>
@@ -6039,20 +6042,48 @@
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr"/>
-      <c r="B17" s="50" t="inlineStr"/>
+      <c r="B17" s="51" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
+          <t>中国クリエイターの登録数を採用計画（入力）に。1期30名</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>工数から導出される数ではない。先に人を集めないと受注できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr"/>
+      <c r="B18" s="51" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>③ の価格を中点から上限に</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>全取引が発注者の支払意思の上限で成約する前提。最も強気の置き方</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr"/>
+      <c r="B19" s="51" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
           <t>管理・コーポレートを6名→3名</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>AX化と BPO。社外の顧問弁護士等が補う前提。その費用が4%に収まるかを検算</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>⚠ 1.4 → 1.5 は構造の作り直し、1.5 → 1.6 は前提を実勢データで詰めたもの。5期の売上は 88.1億 → 108.0億、社員は 61名 → 22名。数字が良くなった分だけ、前提の説明責任が重くなっている。</t>
         </is>
@@ -12034,7 +12065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -12143,23 +12174,23 @@
         <v>950</v>
       </c>
       <c r="C5" s="21">
-        <f>C37</f>
+        <f>C41</f>
         <v/>
       </c>
       <c r="D5" s="21">
-        <f>D37</f>
+        <f>D41</f>
         <v/>
       </c>
       <c r="E5" s="21">
-        <f>E37</f>
+        <f>E41</f>
         <v/>
       </c>
       <c r="F5" s="21">
-        <f>F37</f>
+        <f>F41</f>
         <v/>
       </c>
       <c r="G5" s="21">
-        <f>G37</f>
+        <f>G41</f>
         <v/>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -12449,7 +12480,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>中国クリエイター（稼働・人）</t>
+          <t>中国クリエイター 必要稼働（人）</t>
         </is>
       </c>
       <c r="C17" s="8">
@@ -12481,557 +12512,527 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>中国クリエイター（登録・人）</t>
-        </is>
-      </c>
-      <c r="C18" s="6">
-        <f>C17*2.5</f>
-        <v/>
-      </c>
-      <c r="D18" s="6">
-        <f>D17*2.5</f>
-        <v/>
-      </c>
-      <c r="E18" s="6">
-        <f>E17*2.5</f>
-        <v/>
-      </c>
-      <c r="F18" s="6">
-        <f>F17*2.5</f>
-        <v/>
-      </c>
-      <c r="G18" s="6">
-        <f>G17*2.5</f>
-        <v/>
+          <t>中国クリエイター 登録（人）</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" s="38" t="n">
+        <v>120</v>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>500</v>
+      </c>
+      <c r="F18" s="38" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G18" s="38" t="n">
+        <v>2000</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>稼働の2.5倍★。全員が常時稼働はしない</t>
+          <t>★採用計画。1期30名は松田さんの指示。工数から導出される数ではない</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　稼働率</t>
+        </is>
+      </c>
+      <c r="C19" s="10">
+        <f>IF(C18=0,0,C17/C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="10">
+        <f>IF(D18=0,0,D17/D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>IF(E18=0,0,E17/E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="10">
+        <f>IF(F18=0,0,F17/F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>IF(G18=0,0,G17/G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>必要稼働 ÷ 登録。立ち上げ期は低く、市場が育つと上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 登録数は工数から出る数字ではなく採用計画。先に人を集めないと受注できないので、立ち上げ期は必要稼働より多く抱える。5年で約2,000名（中国の微短劇就業者69万人の0.3%）。年400〜800名を新規登録させる採用オペレーションが要る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>オフショア開発（業務委託）— ベトナム内のピラミッド</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>国・職位</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>月額(万)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>構成比</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>出所・考え方</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>ベトナム ブリッジSE</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="n">
-        <v>59</v>
-      </c>
-      <c r="C21" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>オフショア開発.com 2026。レビューと設計を担う上位層</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>ベトナム プログラマー</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="C22" s="19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>同上。実装を担う</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>インド ブリッジSE</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="C23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>参考。上位層で入れる場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>インド プログラマー</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="C24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>参考。ミドルを別国にすると継ぎ目が増える</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>中国 シニア</t>
+          <t>ベトナム ブリッジSE</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
-        <v>71.7</v>
+        <v>59</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>参考。ベトナムBSEより21%高い</t>
+          <t>オフショア開発.com 2026。レビューと設計を担う上位層</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>ベトナム プログラマー</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>同上。実装を担う</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>インド ブリッジSE</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>参考。上位層で入れる場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>インド プログラマー</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>参考。ミドルを別国にすると継ぎ目が増える</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>中国 シニア</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>参考。ベトナムBSEより21%高い</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>東欧 シニア</t>
         </is>
       </c>
-      <c r="B26" s="25" t="n">
+      <c r="B30" s="25" t="n">
         <v>104</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C30" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>参考。最も高い</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>構成比 合計</t>
         </is>
       </c>
-      <c r="C27" s="38">
-        <f>SUM(C21:C26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="C31" s="39">
+        <f>SUM(C25:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>加重単価（万円/年）</t>
         </is>
       </c>
-      <c r="B28" s="6">
-        <f>SUMPRODUCT(B21:B26,C21:C26)*12</f>
-        <v/>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="B32" s="6">
+        <f>SUMPRODUCT(B25:B30,C25:C30)*12</f>
+        <v/>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>ブリッジSE 20% ＋ プログラマー 80%</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>⚠ ピラミッドはベトナム内で組む。シニアがミドルをレビューする接点は最もコミュニケーション量が多いので、そこに国・言語・ベンダーの継ぎ目を置かない。社員PMの下が2層で収まる。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="37" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>⚠ 安い順は ミャンマー(40)＜インド(45)＜フィリピン(47.5)＜ベトナム(50)＜中国(71.7)＜東欧(104)。ロシア・ベラルーシは外為法の役務取引規制（2022/3/18〜）で対象外。単価の問題ではない。</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>エンジニアのAX化 — 人数を減らして単価の高い層に寄せる</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr"/>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>1期</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>2期</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>3期</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>4期</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>5期</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>考え方</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>必要開発工数（AXなし換算・人年）</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="18" t="n">
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="18" t="n">
+      <c r="D38" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E38" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F38" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="G34" s="18" t="n">
+      <c r="G38" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>★プロダクト規模から</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>★ エンジニアのAX倍率</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="25" t="n">
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="25" t="n">
+      <c r="D39" s="25" t="n">
         <v>1.2</v>
       </c>
-      <c r="E35" s="25" t="n">
+      <c r="E39" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="F35" s="25" t="n">
+      <c r="F39" s="25" t="n">
         <v>1.9</v>
       </c>
-      <c r="G35" s="25" t="n">
+      <c r="G39" s="25" t="n">
         <v>2.2</v>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>★ミドル中心なのでレビューがボトルネックになる。制作(4.0)より低く置く</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>実エンジニア数（委託）</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
-      <c r="C36" s="23">
-        <f>ROUNDUP(C34/C35,0)</f>
-        <v/>
-      </c>
-      <c r="D36" s="23">
-        <f>ROUNDUP(D34/D35,0)</f>
-        <v/>
-      </c>
-      <c r="E36" s="23">
-        <f>ROUNDUP(E34/E35,0)</f>
-        <v/>
-      </c>
-      <c r="F36" s="23">
-        <f>ROUNDUP(F34/F35,0)</f>
-        <v/>
-      </c>
-      <c r="G36" s="23">
-        <f>ROUNDUP(G34/G35,0)</f>
-        <v/>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="23">
+        <f>ROUNDUP(C38/C39,0)</f>
+        <v/>
+      </c>
+      <c r="D40" s="23">
+        <f>ROUNDUP(D38/D39,0)</f>
+        <v/>
+      </c>
+      <c r="E40" s="23">
+        <f>ROUNDUP(E38/E39,0)</f>
+        <v/>
+      </c>
+      <c r="F40" s="23">
+        <f>ROUNDUP(F38/F39,0)</f>
+        <v/>
+      </c>
+      <c r="G40" s="23">
+        <f>ROUNDUP(G38/G39,0)</f>
+        <v/>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>必要工数 ÷ AX倍率</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>PM（社員）</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr"/>
-      <c r="C37" s="23">
-        <f>ROUNDUP(C36/5,0)</f>
-        <v/>
-      </c>
-      <c r="D37" s="23">
-        <f>ROUNDUP(D36/5,0)</f>
-        <v/>
-      </c>
-      <c r="E37" s="23">
-        <f>ROUNDUP(E36/5,0)</f>
-        <v/>
-      </c>
-      <c r="F37" s="23">
-        <f>ROUNDUP(F36/5,0)</f>
-        <v/>
-      </c>
-      <c r="G37" s="23">
-        <f>ROUNDUP(G36/5,0)</f>
-        <v/>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr"/>
+      <c r="C41" s="23">
+        <f>ROUNDUP(C40/5,0)</f>
+        <v/>
+      </c>
+      <c r="D41" s="23">
+        <f>ROUNDUP(D40/5,0)</f>
+        <v/>
+      </c>
+      <c r="E41" s="23">
+        <f>ROUNDUP(E40/5,0)</f>
+        <v/>
+      </c>
+      <c r="F41" s="23">
+        <f>ROUNDUP(F40/5,0)</f>
+        <v/>
+      </c>
+      <c r="G41" s="23">
+        <f>ROUNDUP(G40/5,0)</f>
+        <v/>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>1名で5名を見る。上の人件費表はここを参照</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>開発委託費（百万円）</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr"/>
-      <c r="C38" s="6">
-        <f>C36*$B$28/100</f>
-        <v/>
-      </c>
-      <c r="D38" s="6">
-        <f>D36*$B$28/100</f>
-        <v/>
-      </c>
-      <c r="E38" s="6">
-        <f>E36*$B$28/100</f>
-        <v/>
-      </c>
-      <c r="F38" s="6">
-        <f>F36*$B$28/100</f>
-        <v/>
-      </c>
-      <c r="G38" s="6">
-        <f>G36*$B$28/100</f>
-        <v/>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr"/>
+      <c r="C42" s="6">
+        <f>C40*$B$32/100</f>
+        <v/>
+      </c>
+      <c r="D42" s="6">
+        <f>D40*$B$32/100</f>
+        <v/>
+      </c>
+      <c r="E42" s="6">
+        <f>E40*$B$32/100</f>
+        <v/>
+      </c>
+      <c r="F42" s="6">
+        <f>F40*$B$32/100</f>
+        <v/>
+      </c>
+      <c r="G42" s="6">
+        <f>G40*$B$32/100</f>
+        <v/>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>実人数 × 加重単価</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>旧構成は社員40名。PM4名＋委託19名になる。加重単価は年527万で、中国シニア20%＋ベトナムミドル80%（557万）より安く、継ぎ目もない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="37" t="inlineStr">
-        <is>
-          <t>⚠ 管理・コーポレート3名は、5期に上場会社として内部統制報告制度の対象になる規模には薄い。取引処理はBPOに出す前提だが、内部統制の設計・運用・評価は社員の仕事。監査法人と主幹事に早期に当てること。★確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>社外の専門家を前提にするなら、その費用が見えている必要がある</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>旧構成は社員40名。PM4名＋委託19名になる。加重単価は年527万で、中国シニア20%＋ベトナムミドル80%（557万）より安く、継ぎ目もない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>⚠ 管理・コーポレート3名は、5期に上場会社として内部統制報告制度の対象になる規模には薄い。取引処理はBPOに出す前提だが、内部統制の設計・運用・評価は社員の仕事。監査法人と主幹事に早期に当てること。★確認事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>社外の専門家を前提にするなら、その費用が見えている必要がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>管理3名で回るのは顧問弁護士・監査法人・社労士が外にいるから。その費用は「その他販管費（売上の4%）」に入っている。5期で足りるかの検算。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>費目</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>下限</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>上限</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>監査報酬（上場後）</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>上場会社・売上108億規模</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>株式事務代行・IR</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>信託銀行・開示書類・説明会</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>顧問弁護士</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="C48" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>契約審査・中国パートナー・業務委託設計</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>税理士・社会保険労務士</t>
-        </is>
-      </c>
-      <c r="B49" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="C49" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="H49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>オフィス（社員22名）</t>
+          <t>監査報酬（上場後）</t>
         </is>
       </c>
       <c r="B50" s="18" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C50" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="H50" s="7" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>上場会社・売上108億規模</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>SaaS・通信・インフラ（非開発）</t>
+          <t>株式事務代行・IR</t>
         </is>
       </c>
       <c r="B51" s="18" t="n">
@@ -13040,95 +13041,159 @@
       <c r="C51" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="H51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>信託銀行・開示書類・説明会</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>採用・教育</t>
+          <t>顧問弁護士</t>
         </is>
       </c>
       <c r="B52" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C52" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="C52" s="18" t="n">
-        <v>60</v>
-      </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>PM・統括級の採用は単価が高い</t>
+          <t>契約審査・中国パートナー・業務委託設計</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>旅費交通</t>
+          <t>税理士・社会保険労務士</t>
         </is>
       </c>
       <c r="B53" s="18" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C53" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>ベトナム・インド往復</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
+          <t>オフィス（社員22名）</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>SaaS・通信・インフラ（非開発）</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>採用・教育</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>PM・統括級の採用は単価が高い</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>旅費交通</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>ベトナム・インド往復</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
           <t>保険・その他</t>
         </is>
       </c>
-      <c r="B54" s="18" t="n">
+      <c r="B58" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="C54" s="18" t="n">
+      <c r="C58" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="H54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>合計（百万円）</t>
         </is>
       </c>
-      <c r="B55" s="21">
-        <f>SUM(B46:B54)</f>
-        <v/>
-      </c>
-      <c r="C55" s="21">
-        <f>SUM(C46:C54)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="B59" s="21">
+        <f>SUM(B50:B58)</f>
+        <v/>
+      </c>
+      <c r="C59" s="21">
+        <f>SUM(C50:C58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>その他販管費（5期・売上の4%）</t>
         </is>
       </c>
-      <c r="C56" s="6">
+      <c r="C60" s="6">
         <f>'損益計算書'!G27</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="C57" s="34">
-        <f>IF(C56&gt;=C55,"○ 上限まで賄える","× 足りない")</f>
-        <v/>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="C61" s="34">
+        <f>IF(C60&gt;=C59,"○ 上限まで賄える","× 足りない")</f>
+        <v/>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>★費目はすべて私の見積もり。実際の見積を取ったものではない</t>
         </is>

--- a/事業計画_Ver1.6.xlsx
+++ b/事業計画_Ver1.6.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -229,6 +229,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2359,23 +2362,23 @@
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="40">
+      <c r="C28" s="41">
         <f>SUM(C21:C27)</f>
         <v/>
       </c>
-      <c r="D28" s="40">
+      <c r="D28" s="41">
         <f>SUM(D21:D27)</f>
         <v/>
       </c>
-      <c r="E28" s="40">
+      <c r="E28" s="41">
         <f>SUM(E21:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="40">
+      <c r="F28" s="41">
         <f>SUM(F21:F27)</f>
         <v/>
       </c>
-      <c r="G28" s="40">
+      <c r="G28" s="41">
         <f>SUM(G21:G27)</f>
         <v/>
       </c>
@@ -2415,23 +2418,23 @@
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="41">
+      <c r="C30" s="42">
         <f>IF(C12=0,0,C29/C12)</f>
         <v/>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="42">
         <f>IF(D12=0,0,D29/D12)</f>
         <v/>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="42">
         <f>IF(E12=0,0,E29/E12)</f>
         <v/>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="42">
         <f>IF(F12=0,0,F29/F12)</f>
         <v/>
       </c>
-      <c r="G30" s="41">
+      <c r="G30" s="42">
         <f>IF(G12=0,0,G29/G12)</f>
         <v/>
       </c>
@@ -2714,23 +2717,23 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="40">
+      <c r="C4" s="41">
         <f>'損益計算書'!C29</f>
         <v/>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="41">
         <f>'損益計算書'!D29</f>
         <v/>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="41">
         <f>'損益計算書'!E29</f>
         <v/>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="41">
         <f>'損益計算書'!F29</f>
         <v/>
       </c>
-      <c r="G4" s="40">
+      <c r="G4" s="41">
         <f>'損益計算書'!G29</f>
         <v/>
       </c>
@@ -2902,23 +2905,23 @@
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="40">
+      <c r="C11" s="41">
         <f>C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="41">
         <f>D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="41">
         <f>E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="41">
         <f>F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="41">
         <f>G9+G10</f>
         <v/>
       </c>
@@ -3103,23 +3106,23 @@
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="40">
+      <c r="C19" s="41">
         <f>C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="41">
         <f>D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="41">
         <f>E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="41">
         <f>F16+F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="41">
         <f>G16+G17+G18</f>
         <v/>
       </c>
@@ -3131,23 +3134,23 @@
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="40">
+      <c r="C21" s="41">
         <f>C14+C15+C19</f>
         <v/>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="41">
         <f>D14+D15+D19</f>
         <v/>
       </c>
-      <c r="E21" s="40">
+      <c r="E21" s="41">
         <f>E14+E15+E19</f>
         <v/>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="41">
         <f>F14+F15+F19</f>
         <v/>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="41">
         <f>G14+G15+G19</f>
         <v/>
       </c>
@@ -3599,7 +3602,7 @@
           <t>転換時のシード持分</t>
         </is>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="40">
         <f>C7/C6</f>
         <v/>
       </c>
@@ -3615,7 +3618,7 @@
           <t>シリーズA の持分</t>
         </is>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="40">
         <f>C10/C9</f>
         <v/>
       </c>
@@ -3695,7 +3698,7 @@
           <t>設立（資本金800万）</t>
         </is>
       </c>
-      <c r="C20" s="42" t="inlineStr">
+      <c r="C20" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3720,7 +3723,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="44">
         <f>SUM(D20:H20)</f>
         <v/>
       </c>
@@ -3740,7 +3743,7 @@
           <t>ESOP枠を設計</t>
         </is>
       </c>
-      <c r="C21" s="42" t="inlineStr">
+      <c r="C21" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3765,7 +3768,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="44">
         <f>SUM(D21:H21)</f>
         <v/>
       </c>
@@ -3785,7 +3788,7 @@
           <t>J-KISS 発行（未転換）</t>
         </is>
       </c>
-      <c r="C22" s="42" t="inlineStr">
+      <c r="C22" s="43" t="inlineStr">
         <is>
           <t>1.42億</t>
         </is>
@@ -3810,7 +3813,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="44">
         <f>SUM(D22:H22)</f>
         <v/>
       </c>
@@ -3830,7 +3833,7 @@
           <t>シリーズA ＋ J-KISS転換</t>
         </is>
       </c>
-      <c r="C23" s="42" t="inlineStr">
+      <c r="C23" s="43" t="inlineStr">
         <is>
           <t>3億</t>
         </is>
@@ -3855,7 +3858,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="44">
         <f>SUM(D23:H23)</f>
         <v/>
       </c>
@@ -3875,7 +3878,7 @@
           <t>ESOP補充</t>
         </is>
       </c>
-      <c r="C24" s="42" t="inlineStr">
+      <c r="C24" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3900,7 +3903,7 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="44">
         <f>SUM(D24:H24)</f>
         <v/>
       </c>
@@ -3920,7 +3923,7 @@
           <t>IPO 公募</t>
         </is>
       </c>
-      <c r="C25" s="42" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3945,7 +3948,7 @@
         <f>$C$12</f>
         <v/>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="44">
         <f>SUM(D25:H25)</f>
         <v/>
       </c>
@@ -3965,7 +3968,7 @@
           <t>売出し（既存株主が売る）</t>
         </is>
       </c>
-      <c r="C26" s="42" t="inlineStr">
+      <c r="C26" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3990,7 +3993,7 @@
         <f>H25+$C$13+$C$14</f>
         <v/>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="44">
         <f>SUM(D26:H26)</f>
         <v/>
       </c>
@@ -4048,7 +4051,7 @@
           <t>創業者（役員）</t>
         </is>
       </c>
-      <c r="B30" s="41">
+      <c r="B30" s="42">
         <f>D26</f>
         <v/>
       </c>
@@ -4062,7 +4065,7 @@
           <t>× 除外</t>
         </is>
       </c>
-      <c r="E30" s="41" t="n">
+      <c r="E30" s="42" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="7" t="inlineStr">
@@ -4077,7 +4080,7 @@
           <t>ESOP枠</t>
         </is>
       </c>
-      <c r="B31" s="41">
+      <c r="B31" s="42">
         <f>E26</f>
         <v/>
       </c>
@@ -4091,7 +4094,7 @@
           <t>× 除外</t>
         </is>
       </c>
-      <c r="E31" s="41" t="n">
+      <c r="E31" s="42" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
@@ -4106,7 +4109,7 @@
           <t>シード投資家 保有分</t>
         </is>
       </c>
-      <c r="B32" s="41">
+      <c r="B32" s="42">
         <f>F26</f>
         <v/>
       </c>
@@ -4118,7 +4121,7 @@
         <f>IF(B32&lt;0.1,"○ 算入","× 除外")</f>
         <v/>
       </c>
-      <c r="E32" s="41">
+      <c r="E32" s="42">
         <f>IF(B32&lt;0.1,B32,0)</f>
         <v/>
       </c>
@@ -4134,7 +4137,7 @@
           <t>シリーズA 保有分</t>
         </is>
       </c>
-      <c r="B33" s="41">
+      <c r="B33" s="42">
         <f>G26</f>
         <v/>
       </c>
@@ -4146,7 +4149,7 @@
         <f>IF(B33&lt;0.1,"○ 算入","× 除外")</f>
         <v/>
       </c>
-      <c r="E33" s="41">
+      <c r="E33" s="42">
         <f>IF(B33&lt;0.1,B33,0)</f>
         <v/>
       </c>
@@ -4162,7 +4165,7 @@
           <t>公募・売出し</t>
         </is>
       </c>
-      <c r="B34" s="41">
+      <c r="B34" s="42">
         <f>H26</f>
         <v/>
       </c>
@@ -4176,7 +4179,7 @@
           <t>○ 算入</t>
         </is>
       </c>
-      <c r="E34" s="41">
+      <c r="E34" s="42">
         <f>B34</f>
         <v/>
       </c>
@@ -4207,7 +4210,7 @@
         <f>IF(E35&gt;=0.25,"○ 満たす","× 不足")</f>
         <v/>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="45">
         <f>E35-0.25</f>
         <v/>
       </c>
@@ -4343,7 +4346,7 @@
           <t>転換時のシード持分</t>
         </is>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="40">
         <f>'資本構成の推移'!C15</f>
         <v/>
       </c>
@@ -4369,7 +4372,7 @@
           <t>転換後の希薄化</t>
         </is>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="46">
         <f>B8/B6</f>
         <v/>
       </c>
@@ -4395,7 +4398,7 @@
           <t>上場後のシード持分</t>
         </is>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="40">
         <f>'資本構成の推移'!F25</f>
         <v/>
       </c>
@@ -4517,7 +4520,7 @@
         <f>E13*$B$8</f>
         <v/>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="47">
         <f>F13/$B$5</f>
         <v/>
       </c>
@@ -4554,7 +4557,7 @@
         <f>E14*$B$8</f>
         <v/>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="47">
         <f>F14/$B$5</f>
         <v/>
       </c>
@@ -4587,7 +4590,7 @@
         <f>E15*$B$8</f>
         <v/>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="47">
         <f>F15/$B$5</f>
         <v/>
       </c>
@@ -4664,7 +4667,7 @@
         <f>E19*$B$8</f>
         <v/>
       </c>
-      <c r="G19" s="46">
+      <c r="G19" s="47">
         <f>F19/$B$5</f>
         <v/>
       </c>
@@ -4695,7 +4698,7 @@
         <f>E20*$B$8</f>
         <v/>
       </c>
-      <c r="G20" s="46">
+      <c r="G20" s="47">
         <f>F20/$B$5</f>
         <v/>
       </c>
@@ -4965,7 +4968,7 @@
           <t>Runway</t>
         </is>
       </c>
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>非開示</t>
         </is>
@@ -4992,7 +4995,7 @@
           <t>Technicolor</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>非開示</t>
         </is>
@@ -5014,16 +5017,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="48" t="inlineStr">
         <is>
           <t>【当社 5期（2031年）】</t>
         </is>
       </c>
-      <c r="B14" s="48">
+      <c r="B14" s="49">
         <f>'損益計算書'!$G$12/100</f>
         <v/>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="48" t="inlineStr">
         <is>
           <t>①制作＋②ツール＋③C2C</t>
         </is>
@@ -5113,12 +5116,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>── 実測 ──</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr"/>
+      <c r="B4" s="43" t="inlineStr"/>
       <c r="C4" s="16" t="inlineStr"/>
       <c r="D4" s="7" t="inlineStr"/>
     </row>
@@ -5128,7 +5131,7 @@
           <t>国内 映像制作市場</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>4,580億円</t>
         </is>
@@ -5150,7 +5153,7 @@
           <t>インターネット広告制作費</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>4,922億円</t>
         </is>
@@ -5172,7 +5175,7 @@
           <t>法人数</t>
         </is>
       </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>295万6,717社</t>
         </is>
@@ -5194,7 +5197,7 @@
           <t>中国 剪辑師 平均月給</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>8,935元</t>
         </is>
@@ -5216,7 +5219,7 @@
           <t>中国 微短劇 直接就業者</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>約69万人</t>
         </is>
@@ -5238,7 +5241,7 @@
           <t>Stripe 決済手数料</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>国内カード3.6%／銀行振込1.5%</t>
         </is>
@@ -5260,7 +5263,7 @@
           <t>S3 Standard 東京</t>
         </is>
       </c>
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>1TB/月 ≈ $25</t>
         </is>
@@ -5282,7 +5285,7 @@
           <t>CloudFront 東京</t>
         </is>
       </c>
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>$0.085/GB</t>
         </is>
@@ -5304,7 +5307,7 @@
           <t>ベンチマーク各社の売上</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>業界ベンチマーク シート</t>
         </is>
@@ -5326,7 +5329,7 @@
           <t>東証グロース 上場維持基準</t>
         </is>
       </c>
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
         <is>
           <t>5年経過後 時価総額100億円</t>
         </is>
@@ -5343,12 +5346,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>── 確認できなかった ──</t>
         </is>
       </c>
-      <c r="B15" s="42" t="inlineStr"/>
+      <c r="B15" s="43" t="inlineStr"/>
       <c r="C15" s="16" t="inlineStr"/>
       <c r="D15" s="7" t="inlineStr"/>
     </row>
@@ -5358,7 +5361,7 @@
           <t>スキルシェア市場の映像比率</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>非公表</t>
         </is>
@@ -5375,12 +5378,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>── 松田さんの決定 ──</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr"/>
+      <c r="B17" s="43" t="inlineStr"/>
       <c r="C17" s="16" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr"/>
     </row>
@@ -5390,7 +5393,7 @@
           <t>③ 手数料率</t>
         </is>
       </c>
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>一律30%（クリエイター70%）</t>
         </is>
@@ -5412,7 +5415,7 @@
           <t>③ 送金・為替</t>
         </is>
       </c>
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -5434,7 +5437,7 @@
           <t>③ 成約位置</t>
         </is>
       </c>
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>均等（価格帯の中点）</t>
         </is>
@@ -5456,7 +5459,7 @@
           <t>① クリエイター支払</t>
         </is>
       </c>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>厚いまま（実効時給3,000〜6,000円）</t>
         </is>
@@ -5478,7 +5481,7 @@
           <t>②-C セルフサーブ</t>
         </is>
       </c>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>②に置く／用途特化</t>
         </is>
@@ -5495,12 +5498,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="49" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>── ★私が置いた値 ──</t>
         </is>
       </c>
-      <c r="B23" s="42" t="inlineStr"/>
+      <c r="B23" s="43" t="inlineStr"/>
       <c r="C23" s="16" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr"/>
     </row>
@@ -5510,7 +5513,7 @@
           <t>AX倍率</t>
         </is>
       </c>
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B24" s="43" t="inlineStr">
         <is>
           <t>1.0 → 4.0倍</t>
         </is>
@@ -5532,7 +5535,7 @@
           <t>① 商品の値引率</t>
         </is>
       </c>
-      <c r="B25" s="42" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>一律50%</t>
         </is>
@@ -5554,7 +5557,7 @@
           <t>① 難度係数</t>
         </is>
       </c>
-      <c r="B26" s="42" t="inlineStr">
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>3.0 / 1.8 / 1.0 / 0.8</t>
         </is>
@@ -5576,7 +5579,7 @@
           <t>① 商品構成比</t>
         </is>
       </c>
-      <c r="B27" s="42" t="inlineStr">
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>年を追って上位帯へシフト</t>
         </is>
@@ -5598,7 +5601,7 @@
           <t>① 営業の担当社数・リピート</t>
         </is>
       </c>
-      <c r="B28" s="42" t="inlineStr">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>40社／年6本</t>
         </is>
@@ -5620,7 +5623,7 @@
           <t>② SKU単価・席数・Ent比率</t>
         </is>
       </c>
-      <c r="B29" s="42" t="inlineStr">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>商品マスタ② 参照</t>
         </is>
@@ -5642,7 +5645,7 @@
           <t>③ 工数・上限価格・件数</t>
         </is>
       </c>
-      <c r="B30" s="42" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>商品マスタ③ 参照</t>
         </is>
@@ -5664,7 +5667,7 @@
           <t>③ システム原価の内訳</t>
         </is>
       </c>
-      <c r="B31" s="42" t="inlineStr">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>尺・保管期間・トークン数</t>
         </is>
@@ -5686,7 +5689,7 @@
           <t>希薄化係数</t>
         </is>
       </c>
-      <c r="B32" s="42" t="inlineStr">
+      <c r="B32" s="43" t="inlineStr">
         <is>
           <t>資本構成の推移 参照</t>
         </is>
@@ -5703,12 +5706,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="49" t="inlineStr">
+      <c r="A33" s="50" t="inlineStr">
         <is>
           <t>── 未確定 ──</t>
         </is>
       </c>
-      <c r="B33" s="42" t="inlineStr"/>
+      <c r="B33" s="43" t="inlineStr"/>
       <c r="C33" s="16" t="inlineStr"/>
       <c r="D33" s="7" t="inlineStr"/>
     </row>
@@ -5718,7 +5721,7 @@
           <t>中国の映像制作パートナー</t>
         </is>
       </c>
-      <c r="B34" s="42" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>社名 ［記入予定］</t>
         </is>
@@ -5740,7 +5743,7 @@
           <t>パートナーの取り分</t>
         </is>
       </c>
-      <c r="B35" s="42" t="inlineStr">
+      <c r="B35" s="43" t="inlineStr">
         <is>
           <t>30%側か70%側か</t>
         </is>
@@ -5762,7 +5765,7 @@
           <t>業務委託の契約設計</t>
         </is>
       </c>
-      <c r="B36" s="42" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>─</t>
         </is>
@@ -5835,12 +5838,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr">
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5858,7 +5861,7 @@
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr"/>
-      <c r="B5" s="51" t="inlineStr"/>
+      <c r="B5" s="52" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>市場規模の次に「業界の売上」を新設</t>
@@ -5871,12 +5874,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5894,7 +5897,7 @@
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr"/>
-      <c r="B7" s="51" t="inlineStr"/>
+      <c r="B7" s="52" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>① 単価を「企業の現行支払×50%」に。本数は営業体制から</t>
@@ -5908,7 +5911,7 @@
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr"/>
-      <c r="B8" s="51" t="inlineStr"/>
+      <c r="B8" s="52" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>② 5SKU・法人2階建て・②-Cセルフサーブを新設</t>
@@ -5922,7 +5925,7 @@
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr"/>
-      <c r="B9" s="51" t="inlineStr"/>
+      <c r="B9" s="52" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>③ 14商品。下限はクリエイターの留保価格、上限は日本の支払意思</t>
@@ -5935,12 +5938,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="B10" s="51" t="inlineStr">
+      <c r="B10" s="52" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -5958,7 +5961,7 @@
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr"/>
-      <c r="B11" s="51" t="inlineStr"/>
+      <c r="B11" s="52" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
           <t>③ 手数料を一律30%に。30%から決済・送金・システム原価を引く</t>
@@ -5972,7 +5975,7 @@
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr"/>
-      <c r="B12" s="51" t="inlineStr"/>
+      <c r="B12" s="52" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>③ システム原価を商品別に積み上げ（120円→53円）</t>
@@ -5986,7 +5989,7 @@
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr"/>
-      <c r="B13" s="51" t="inlineStr"/>
+      <c r="B13" s="52" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>② ACVとARRを分離。①③のARRはゼロと明示</t>
@@ -6000,7 +6003,7 @@
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr"/>
-      <c r="B14" s="51" t="inlineStr"/>
+      <c r="B14" s="52" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>エンジニアを社員40名 → PM4名＋ベトナム委託19名</t>
@@ -6014,7 +6017,7 @@
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr"/>
-      <c r="B15" s="51" t="inlineStr"/>
+      <c r="B15" s="52" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>エンジニアにもAX倍率（5期2.2倍）</t>
@@ -6028,7 +6031,7 @@
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr"/>
-      <c r="B16" s="51" t="inlineStr"/>
+      <c r="B16" s="52" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>中国・東欧・ロシアを委託先から外す</t>
@@ -6042,7 +6045,7 @@
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr"/>
-      <c r="B17" s="51" t="inlineStr"/>
+      <c r="B17" s="52" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
           <t>中国クリエイターの登録数を採用計画（入力）に。1期30名</t>
@@ -6056,7 +6059,7 @@
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr"/>
-      <c r="B18" s="51" t="inlineStr"/>
+      <c r="B18" s="52" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>③ の価格を中点から上限に</t>
@@ -6070,7 +6073,7 @@
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr"/>
-      <c r="B19" s="51" t="inlineStr"/>
+      <c r="B19" s="52" t="inlineStr"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>管理・コーポレートを6名→3名</t>
@@ -6083,7 +6086,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>⚠ 1.4 → 1.5 は構造の作り直し、1.5 → 1.6 は前提を実勢データで詰めたもの。5期の売上は 88.1億 → 108.0億、社員は 61名 → 22名。数字が良くなった分だけ、前提の説明責任が重くなっている。</t>
         </is>
@@ -10761,7 +10764,7 @@
         <v>1.5</v>
       </c>
       <c r="E5" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D5/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D5/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F5" s="6" t="n">
@@ -10806,7 +10809,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D6/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D6/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F6" s="6" t="n">
@@ -10851,7 +10854,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D7/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D7/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F7" s="6" t="n">
@@ -10896,7 +10899,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D8/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D8/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F8" s="6" t="n">
@@ -10941,7 +10944,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D9/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D9/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F9" s="6" t="n">
@@ -10986,7 +10989,7 @@
         <v>15</v>
       </c>
       <c r="E10" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D10/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D10/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F10" s="6" t="n">
@@ -11031,7 +11034,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D11/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D11/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F11" s="6" t="n">
@@ -11076,7 +11079,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D12/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D12/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F12" s="6" t="n">
@@ -11121,7 +11124,7 @@
         <v>14</v>
       </c>
       <c r="E13" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D13/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D13/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F13" s="6" t="n">
@@ -11166,7 +11169,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D14/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D14/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F14" s="6" t="n">
@@ -11211,7 +11214,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D15/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D15/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F15" s="6" t="n">
@@ -11256,7 +11259,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D16/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D16/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F16" s="6" t="n">
@@ -11301,7 +11304,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D17/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D17/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F17" s="6" t="n">
@@ -11346,7 +11349,7 @@
         <v>50</v>
       </c>
       <c r="E18" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D18/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D18/(1-$B$28)/500,0)*500</f>
         <v/>
       </c>
       <c r="F18" s="6" t="n">
@@ -11448,7 +11451,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>合計</t>
+          <t>合計（②-Cの共食い前）</t>
         </is>
       </c>
       <c r="H23" s="6">
@@ -11464,62 +11467,82 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　− ②-Cセルフサーブによる共食い（③-A）</t>
+        </is>
+      </c>
+      <c r="J24" s="36">
+        <f>-J20*G35</f>
+        <v/>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>③-Aの安い帯が②-Cに流れる分。下の期別GMVはこれを引いた後</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>5期GMV（共食い後）＝下の期別G列と一致</t>
+        </is>
+      </c>
+      <c r="J25" s="31">
+        <f>J23+J24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>手数料と原価率</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>手数料率</t>
-        </is>
-      </c>
-      <c r="B26" s="36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>一律30%。70%をクリエイターに渡す（松田さん決定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>決済手数料率</t>
-        </is>
-      </c>
-      <c r="B27" s="36" t="n">
-        <v>0.0318</v>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>Stripe 国内カード3.6%／銀行振込1.5% を 80:20 で加重</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>送金・為替</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="n">
+          <t>手数料率</t>
+        </is>
+      </c>
+      <c r="B28" s="37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>一律30%。70%をクリエイターに渡す（松田さん決定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>決済手数料率</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Stripe 国内カード3.6%／銀行振込1.5% を 80:20 で加重</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>期別</t>
+        </is>
+      </c>
+      <c r="B30" s="37" t="n">
         <v>0.03</v>
       </c>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>中国の制作パートナー経由（松田さん指示）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>期別</t>
         </is>
       </c>
     </row>
@@ -11823,23 +11846,23 @@
       </c>
       <c r="B41" s="5" t="inlineStr"/>
       <c r="C41" s="6">
-        <f>C39*$B$26</f>
+        <f>C39*$B$28</f>
         <v/>
       </c>
       <c r="D41" s="6">
-        <f>D39*$B$26</f>
+        <f>D39*$B$28</f>
         <v/>
       </c>
       <c r="E41" s="6">
-        <f>E39*$B$26</f>
+        <f>E39*$B$28</f>
         <v/>
       </c>
       <c r="F41" s="6">
-        <f>F39*$B$26</f>
+        <f>F39*$B$28</f>
         <v/>
       </c>
       <c r="G41" s="6">
-        <f>G39*$B$26</f>
+        <f>G39*$B$28</f>
         <v/>
       </c>
     </row>
@@ -11851,23 +11874,23 @@
       </c>
       <c r="B42" s="5" t="inlineStr"/>
       <c r="C42" s="23">
-        <f>C39*($B$27+$B$28)+C40*'システム原価'!$H$29/1000000</f>
+        <f>C39*($B$29+$B$30)+C40*'システム原価'!$H$29/1000000</f>
         <v/>
       </c>
       <c r="D42" s="23">
-        <f>D39*($B$27+$B$28)+D40*'システム原価'!$H$29/1000000</f>
+        <f>D39*($B$29+$B$30)+D40*'システム原価'!$H$29/1000000</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>E39*($B$27+$B$28)+E40*'システム原価'!$H$29/1000000</f>
+        <f>E39*($B$29+$B$30)+E40*'システム原価'!$H$29/1000000</f>
         <v/>
       </c>
       <c r="F42" s="23">
-        <f>F39*($B$27+$B$28)+F40*'システム原価'!$H$29/1000000</f>
+        <f>F39*($B$29+$B$30)+F40*'システム原価'!$H$29/1000000</f>
         <v/>
       </c>
       <c r="G42" s="23">
-        <f>G39*($B$27+$B$28)+G40*'システム原価'!$H$29/1000000</f>
+        <f>G39*($B$29+$B$30)+G40*'システム原価'!$H$29/1000000</f>
         <v/>
       </c>
     </row>
@@ -11928,7 +11951,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="37" t="inlineStr">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t>⚠ 全商品が上限で成約する前提。下限（クリエイターの留保価格）との差がそのまま利幅になる。供給が厚いほど競争で下限側に寄るのが市場の常なので、ここは最も強気の置き方。中点なら③のGMVは約57%、全部が下限なら約5%になる。</t>
         </is>
@@ -12515,19 +12538,19 @@
           <t>中国クリエイター 登録（人）</t>
         </is>
       </c>
-      <c r="C18" s="38" t="n">
+      <c r="C18" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="38" t="n">
+      <c r="D18" s="39" t="n">
         <v>120</v>
       </c>
-      <c r="E18" s="38" t="n">
+      <c r="E18" s="39" t="n">
         <v>500</v>
       </c>
-      <c r="F18" s="38" t="n">
+      <c r="F18" s="39" t="n">
         <v>1200</v>
       </c>
-      <c r="G18" s="38" t="n">
+      <c r="G18" s="39" t="n">
         <v>2000</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -12722,7 +12745,7 @@
           <t>構成比 合計</t>
         </is>
       </c>
-      <c r="C31" s="39">
+      <c r="C31" s="40">
         <f>SUM(C25:C30)</f>
         <v/>
       </c>
@@ -12751,7 +12774,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="A34" s="38" t="inlineStr">
         <is>
           <t>⚠ 安い順は ミャンマー(40)＜インド(45)＜フィリピン(47.5)＜ベトナム(50)＜中国(71.7)＜東欧(104)。ロシア・ベラルーシは外為法の役務取引規制（2022/3/18〜）で対象外。単価の問題ではない。</t>
         </is>
@@ -12965,7 +12988,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="37" t="inlineStr">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t>⚠ 管理・コーポレート3名は、5期に上場会社として内部統制報告制度の対象になる規模には薄い。取引処理はBPOに出す前提だが、内部統制の設計・運用・評価は社員の仕事。監査法人と主幹事に早期に当てること。★確認事項</t>
         </is>
